--- a/packaging_master.xlsx
+++ b/packaging_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hemcorporation-my.sharepoint.com/personal/analytics_hemcorporation_onmicrosoft_com/Documents/Exports Product Catalogue Project/CatalogueMaker/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aeea0f31faf7c20a/Documents/GitHub/hem-catalogue-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC1048D5B91F41405BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{813F1FBE-F8F3-463D-8939-130B66A23336}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC1048D5B91F41405BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8142A260-D6D3-4767-8029-8C2334B8A3B2}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="11466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -454,7 +454,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>12</v>
